--- a/docs/ubwc_reg_table_cn.xlsx
+++ b/docs/ubwc_reg_table_cn.xlsx
@@ -67,7 +67,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -512,7 +512,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0x000C</t>
+          <t>0x000c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0x000C</t>
+          <t>0x000c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>0x000C</t>
+          <t>0x000c</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>tile 高度，单位像素；RGBA=4，YUV420=8。</t>
+          <t>tile 高度，单位像素；RGBA=4，YUV420_8=8，YUV420_10=4。</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>0x002C</t>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>0x002C</t>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>0x003C</t>
+          <t>0x003c</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>0x004C</t>
+          <t>0x004c</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>0x005C</t>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3050,42 +3050,42 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>只读</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>写 1 脉冲</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>start</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>中断状态位图。</t>
+          <t>帧 START 写 1 脉冲；地址组写完后再写该 bit 启动本帧。</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>运行中或中断后读取，用于调试和状态确认。</t>
+          <t>每帧地址组写完整后写 1；读回为 0。地址写入不再单独启动帧。</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>中断状态位图。</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>只读状态或统计信息。</t>
+          <t>运行中或中断后读取，用于调试和状态确认。</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>0x0069</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>0x006A</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x006B</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x006C</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x006D</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x006E</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x006F</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x0071</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x0072</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0073</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x0094</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3708,54 +3708,101 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x0075</t>
+          <t>0x0098</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>只读</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>只读状态或统计信息。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>0x009c</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>只读</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>dynamic</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
         <is>
           <t>只读状态或统计信息。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I78"/>
+  <autoFilter ref="A1:I79"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -4247,7 +4294,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0x000C</t>
+          <t>0x000c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4623,7 +4670,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4670,7 +4717,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4999,7 +5046,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>0x002C</t>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5046,7 +5093,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>0x002C</t>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5234,7 +5281,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>0x003C</t>
+          <t>0x003c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5422,7 +5469,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>0x004C</t>
+          <t>0x004c</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5939,7 +5986,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>0x005C</t>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6221,42 +6268,42 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS4</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>只读</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>写 1 脉冲</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>start</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>中断状态位图。</t>
+          <t>帧 START 写 1 脉冲；地址组写完后再写该 bit 启动本帧。</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>运行中或中断后读取，用于调试和状态确认。</t>
+          <t>每帧地址组写完整后写 1；读回为 0。地址写入不再单独启动帧。</t>
         </is>
       </c>
     </row>
@@ -6268,12 +6315,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>APB_ADDR_STAT_META</t>
+          <t>APB_ADDR_STATUS4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6288,17 +6335,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stat_meta_tile_cnt</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>DEC metadata 有效 tile 计数。</t>
+          <t>中断状态位图。</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6315,12 +6362,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>0x006C</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>APB_ADDR_STAT_TILE</t>
+          <t>APB_ADDR_STAT_META</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6340,12 +6387,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stat_tile_addr_cnt</t>
+          <t>stat_meta_tile_cnt</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>DEC tile 地址生成有效 tile 计数。</t>
+          <t>DEC metadata 有效 tile 计数。</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6362,12 +6409,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>APB_ADDR_STAT_OTF_TILE</t>
+          <t>APB_ADDR_STAT_TILE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6387,12 +6434,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stat_otf_tile_cnt</t>
+          <t>stat_tile_addr_cnt</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>DEC tile-to-OTF 接收 tile 计数。</t>
+          <t>DEC tile 地址生成有效 tile 计数。</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6409,12 +6456,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>APB_ADDR_STAT_OTF_LINE</t>
+          <t>APB_ADDR_STAT_OTF_TILE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6434,12 +6481,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stat_otf_line_cnt</t>
+          <t>stat_otf_tile_cnt</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>DEC OTF 输出行计数。</t>
+          <t>DEC tile-to-OTF 接收 tile 计数。</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6456,47 +6503,94 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
+          <t>0x0074</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>APB_ADDR_STAT_OTF_LINE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>只读</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>stat_otf_line_cnt</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>DEC OTF 输出行计数。</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>运行中或中断后读取，用于调试和状态确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>0x0078</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>APB_ADDR_STAT_OTF_DE</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>只读</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>dynamic</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>stat_otf_de_cnt</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>DEC OTF 输出 de &amp;&amp; ready 有效 beat 计数。</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>运行中或中断后读取，用于调试和状态确认。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I58"/>
+  <autoFilter ref="A1:I59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6525,7 +6619,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-07 04:34:29</t>
+          <t>2026-05-14 22:08:50</t>
         </is>
       </c>
     </row>
@@ -6952,7 +7046,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>配置 tile_w 和 tile_h。RGBA=16x4，YUV420=32x8。</t>
+          <t>配置 tile_w 和 tile_h。RGBA=16x4，YUV420_8=32x8，YUV420_10=32x4。</t>
         </is>
       </c>
     </row>
@@ -7267,12 +7361,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Start OTF input stream</t>
+          <t>WRITE 0x060 bit[5]=1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENC 没有 APB start。上游 OTF vsync/hsync/de/data 进入后开始处理；fcnt[0] 用于选择地址 slot 和 sideband。</t>
+          <t>写 START token。地址写入只填充地址队列，不再作为 start 标志；写 START 后再送入对应 OTF vsync/hsync/de/data。</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7526,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>配置 CI input type、sideband、lossy、alpha mode。当前 tiled UBWC 流通常写 input_type=1。</t>
+          <t>配置 CI input type、lossy、alpha mode。当前 tiled UBWC 流通常写 input_type=1。</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7821,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEC 自动启动</t>
+          <t>DEC 启动</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7737,7 +7831,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>硬件自动</t>
+          <t>每帧</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7747,12 +7841,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>不需要 APB start</t>
+          <t>WRITE 0x060 bit[5]=1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>完整地址组有效、metadata 不 busy、launch slot 可用时，硬件自动锁存本帧地址，产生 frame_start 并启动 decode。</t>
+          <t>写 START token。完整地址组和 START token 都有效，且 metadata stage 可接受新帧时，硬件锁存本帧地址并启动 decode。</t>
         </is>
       </c>
     </row>
@@ -8091,12 +8185,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEC 自动启动</t>
+          <t>DEC START</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>完整 DEC 地址组有效、metadata 不 busy、launch slot 可用时，硬件自动锁存本帧地址并启动 decode。</t>
+          <t>完整 DEC 地址组和 START token 都有效、metadata 不 busy、launch slot 可用时，硬件锁存本帧地址并启动 decode。</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8214,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>correct IRQ 在帧末倒数第 4 行 hsync 附近产生；error IRQ 在错误条件锁存时产生。</t>
+          <t>correct IRQ/frame_done 在最后一个有效帧输出/数据完成事件后产生；error IRQ 在错误条件锁存时产生。</t>
         </is>
       </c>
     </row>

--- a/docs/ubwc_reg_table_cn.xlsx
+++ b/docs/ubwc_reg_table_cn.xlsx
@@ -67,7 +67,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I81"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>错误状态位。</t>
+          <t>metadata co-buffer overflow 错误状态。</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>错误状态位。</t>
+          <t>metadata tile order 错误状态。</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>0x005c</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>REG_STATUS1</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2788,22 +2788,22 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7:0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stage_done</t>
+          <t>addr_cfg_overflow</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stage done 位图。</t>
+          <t>ENC 地址 slot FIFO overflow 粘性状态。</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>运行中读取。</t>
+          <t>只读状态或统计信息。</t>
         </is>
       </c>
     </row>
@@ -2815,42 +2815,42 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>REG_IRQ_CTRL</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>读写</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>0x00000001</t>
+          <t>只读</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>irq_enable</t>
+          <t>rst_drain_timeout</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>中断使能。</t>
+          <t>ENC 软复位等待 AXI drain 超时状态。</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>上电后或中断策略变化时配置。</t>
+          <t>只读状态或统计信息。</t>
         </is>
       </c>
     </row>
@@ -2862,42 +2862,42 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>REG_IRQ_CTRL</t>
+          <t>REG_STATUS1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>写 1 脉冲</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>只读</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7:0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>irq_clear</t>
+          <t>stage_done</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>中断清除写 1 脉冲。</t>
+          <t>stage done 位图。</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>软件处理中断后写 1；读回为 0。</t>
+          <t>运行中读取。</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>只读</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>读写</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>irq_pending</t>
+          <t>irq_enable</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>任意中断 pending 状态。</t>
+          <t>中断使能。</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>运行中或中断后读取，用于调试和状态确认。</t>
+          <t>上电后或中断策略变化时配置。</t>
         </is>
       </c>
     </row>
@@ -2966,32 +2966,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>只读</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>写 1 脉冲</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>irq_correct_pending</t>
+          <t>irq_clear</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>正确完成中断 pending 状态。</t>
+          <t>中断清除写 1 脉冲。</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>运行中或中断后读取，用于调试和状态确认。</t>
+          <t>软件处理中断后写 1；读回为 0。</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>irq_error_pending</t>
+          <t>irq_pending</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>错误状态位。</t>
+          <t>任意中断 pending 状态。</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3060,32 +3060,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>写 1 脉冲</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>只读</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>irq_correct_pending</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>帧 START 写 1 脉冲；地址组写完后再写该 bit 启动本帧。</t>
+          <t>正确完成中断 pending 状态。</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>每帧地址组写完整后写 1；读回为 0。地址写入不再单独启动帧。</t>
+          <t>运行中或中断后读取，用于调试和状态确认。</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3117,17 +3117,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>irq_error_pending</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>中断状态位图。</t>
+          <t>错误状态位。</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3144,42 +3144,42 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>只读</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>写 1 脉冲</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>start</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>帧 START 写 1 脉冲；地址组写完后再写该 bit 启动本帧。</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>只读状态或统计信息。</t>
+          <t>每帧地址组写完整后写 1；读回为 0。地址写入不再单独启动帧。</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>0x006c</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3211,22 +3211,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>中断状态位图。</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>只读状态或统计信息。</t>
+          <t>运行中或中断后读取，用于调试和状态确认。</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x0078</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x007c</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x0080</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x0084</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x0088</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x008c</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0090</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x0094</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x0098</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3755,47 +3755,141 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
+          <t>0x0094</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>REG_TILE_AXI_W_CNT1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>只读</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>只读状态或统计信息。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>只读</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>只读状态或统计信息。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>0x009c</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>只读</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>dynamic</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>只读状态或统计信息。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I79"/>
+  <autoFilter ref="A1:I81"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5959,17 +6053,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>6:0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>vivo_idle_bits</t>
+          <t>vivo_idle</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>对应模块或整体流水线 idle 状态。</t>
+          <t>VIVO idle 状态。</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6006,17 +6100,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>6:0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>vivo_error_bits</t>
+          <t>vivo_error</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>错误状态位。</t>
+          <t>VIVO error 状态。</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6619,7 +6713,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-14 22:08:50</t>
+          <t>2026-05-19 09:33:12</t>
         </is>
       </c>
     </row>

--- a/docs/ubwc_reg_table_cn.xlsx
+++ b/docs/ubwc_reg_table_cn.xlsx
@@ -67,7 +67,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CI 输入类型配置；tiled UBWC 数据通常写 1。</t>
+          <t>CI input type 配置；1=tiled data，0=linear data；寄存器复位值为 0，普通 tiled UBWC 路径软件应配置为 1。</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CI AXI burst length/ALEN 配置。</t>
+          <t>CI alen 配置；寄存器复位值为 0，普通 VIVO_ENC 配置软件应写 7。</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[31:0]</t>
+          <t>meta_y_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[63:32]</t>
+          <t>meta_y_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[31:0]</t>
+          <t>y_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[63:32]</t>
+          <t>y_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[31:0]</t>
+          <t>meta_uv_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[63:32]</t>
+          <t>meta_uv_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[31:0]</t>
+          <t>uv_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[63:32]</t>
+          <t>uv_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2217,9 +2217,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2264,9 +2264,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2311,9 +2311,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2358,9 +2358,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2405,9 +2405,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2452,9 +2452,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2499,9 +2499,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2546,9 +2546,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2593,9 +2593,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2640,9 +2640,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>当前 fcnt[0] 对应地址 slot 未配置，数据会被阻塞并上报错误。</t>
+          <t>当前 slot 地址未配置错误 sticky 状态；ENC 数据链路按当前帧 fcnt[0] 选择 slot0 或 slot1 的地址配置。当硬件检查当前 slot 地址有效性时，如果被选中的地址 FIFO 为空，则 active_addr_cfg_valid 为 0，该 bit 置 1 并保持，同时参与 error IRQ。该状态表示当前帧没有可用的 META/TILE 基地址，软件必须先补齐对应 slot 的每帧地址组，确认 buffer 队列与 fcnt[0] 对齐后，再写 REG_IRQ_CTRL[1] irq_clear 清 sticky 状态；关闭 enc_ubwc_en 或硬复位也会清零。</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2687,9 +2687,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2734,9 +2734,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2781,9 +2781,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ENC 地址 slot FIFO overflow 粘性状态。</t>
+          <t>地址配置 FIFO overflow sticky 状态；ENC 每帧地址由 META Y、TILE Y、META UV、TILE UV 四个 64-bit 基地址组成，软件写 REG_TILE_BASE_UV_HI 作为一次地址组 commit。APB block 会按 slot0/slot1 轮流把地址组写入对应地址 FIFO，每个 slot FIFO 深度为 4。当 commit 时选中的 slot FIFO 已满，当前地址组不会 push 进 FIFO，该 bit 置 1 并保持，同时参与 error IRQ。软件应停止继续提交地址，等待已有帧消耗地址 FIFO；若已发生 overflow，应写 REG_IRQ_CTRL[1] irq_clear 清 sticky 状态，并确认软件 buffer 队列与硬件地址队列重新对齐，必要时关闭 enc_ubwc_en 后重新配置。</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2828,9 +2828,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ENC 软复位等待 AXI drain 超时状态。</t>
+          <t>软复位等待 AXI drain 超时 sticky 状态；ENC 进入 soft reset 前会停止发起新的 AXI 写事务，并等待 tile/meta AXI 写通路 outstanding 清空。如果等待超过 16'hffff 个 i_axi_clk 周期仍未进入 idle，则该 bit 置 1 并保持；软件写 REG_IRQ_CTRL[1] irq_clear 或硬复位后清零。</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2875,9 +2875,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>中断使能。</t>
+          <t>中断使能；寄存器复位值为 0，需要中断输出时软件应配置为 1。</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3016,9 +3016,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3063,9 +3063,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3110,9 +3110,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3191,42 +3191,42 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>只读</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>读写</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>vsync_reset_en</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>中断状态位图。</t>
+          <t>ENC 输入 VSYNC 上升沿触发整条 ENC 链路软复位；复位通过 AXI drain reset sequencer 执行。</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>运行中或中断后读取，用于调试和状态确认。</t>
+          <t>按系统策略配置；置 1 后 ENC 输入 VSYNC 上升沿会触发软复位并重新 arm frame start。</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3251,29 +3251,29 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>中断状态位图。</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>只读状态或统计信息。</t>
+          <t>运行中或中断后读取，用于调试和状态确认。</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x006c</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3298,9 +3298,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3345,9 +3345,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3392,9 +3392,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x0078</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3439,9 +3439,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x007c</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3486,9 +3486,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x0080</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x0084</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3580,9 +3580,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0088</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3627,9 +3627,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x008c</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3674,9 +3674,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x0090</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3721,9 +3721,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>0x0094</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3768,9 +3768,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>0x0098</t>
+          <t>0x0094</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3815,9 +3815,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3849,47 +3849,94 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>只读</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>只读状态或统计信息。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>0x009c</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>只读</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>dynamic</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>只读状态或统计信息。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I81"/>
+  <autoFilter ref="A1:I82"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4465,7 +4512,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CI 输入类型配置；tiled UBWC 数据通常写 1。</t>
+          <t>CI input type 配置；1=tiled data，0=linear data；寄存器复位值为 0，普通 tiled UBWC 路径软件应配置为 1。</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4591,7 +4638,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5259,7 +5306,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_y[31:0]</t>
+          <t>meta_base_addr_rgba_y_31_0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5306,7 +5353,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_y[63:32]</t>
+          <t>meta_base_addr_rgba_y_63_32</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5353,7 +5400,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tile_base_addr_rgba_y[31:0]</t>
+          <t>tile_base_addr_rgba_y_31_0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5400,7 +5447,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tile_base_addr_rgba_y[63:32]</t>
+          <t>tile_base_addr_rgba_y_63_32</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5447,7 +5494,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>meta_base_addr_uv[31:0]</t>
+          <t>meta_base_addr_uv_31_0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5494,7 +5541,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>meta_base_addr_uv[63:32]</t>
+          <t>meta_base_addr_uv_63_32</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5541,7 +5588,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tile_base_addr_uv[31:0]</t>
+          <t>tile_base_addr_uv_31_0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5588,7 +5635,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tile_base_addr_uv[63:32]</t>
+          <t>tile_base_addr_uv_63_32</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5623,9 +5670,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5670,9 +5717,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5717,9 +5764,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5764,9 +5811,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5811,9 +5858,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5858,9 +5905,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5905,9 +5952,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5952,9 +5999,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5999,9 +6046,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6046,9 +6093,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6093,9 +6140,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6142,7 +6189,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6157,7 +6204,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>中断使能。</t>
+          <t>中断使能；寄存器复位值为 0，需要中断输出时软件应配置为 1。</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6234,9 +6281,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6281,9 +6328,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6328,9 +6375,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6422,9 +6469,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6469,9 +6516,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6516,9 +6563,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6563,9 +6610,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6610,9 +6657,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6657,9 +6704,9 @@
           <t>只读</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6713,7 +6760,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 09:33:12</t>
+          <t>2026-05-21 13:09:24</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6931,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>使能中断。ENC IRQ_CTRL 地址为 0x060，DEC IRQ_CTRL 地址为 0x060。复位默认 irq_enable=1。</t>
+          <t>使能中断。ENC IRQ_CTRL 地址为 0x060，DEC IRQ_CTRL 地址为 0x060。寄存器复位值为 0，软件需要写 1 才使能 IRQ。</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7123,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>最后写 CI_CFG0，配置 enc_ci_input_type 和 enc_ci_alen。当前软件通常写 input_type=1、alen=7。</t>
+          <t>最后写 CI_CFG0；寄存器复位值为 0，普通 tiled UBWC 路径软件应配置 enc_ci_input_type=1、enc_ci_alen=7。</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7539,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应地址 slot 未配置。IRQ bit 区分 correct/error pending。</t>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应 slot 没有可用地址配置，是 sticky 错误状态；软件补齐地址并确认队列对齐后，通过 REG_IRQ_CTRL[1] irq_clear 清除。IRQ bit 区分 correct/error pending。</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7667,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>配置 CI input type、lossy、alpha mode。当前 tiled UBWC 流通常写 input_type=1。</t>
+          <t>配置 CI input type、lossy、alpha mode。寄存器复位值为 0，普通 tiled UBWC 路径软件应配置 ci_input_type=1。</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7699,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>配置 vivo_ubwc_en 和 vivo_sreset。通常 vivo_ubwc_en 复位后保持 1。</t>
+          <t>配置 vivo_ubwc_en 和 vivo_sreset。寄存器复位值为 0，启动 decode 前软件应配置 vivo_ubwc_en=1。</t>
         </is>
       </c>
     </row>

--- a/docs/ubwc_reg_table_cn.xlsx
+++ b/docs/ubwc_reg_table_cn.xlsx
@@ -67,7 +67,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>每帧配置，低/高 32 bit 共同组成 64 bit base 地址。</t>
+          <t>地址或 layout 变化时配置；低/高 32 bit 共同组成唯一地址组中的一个 64 bit base 地址。</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>每帧配置，低/高 32 bit 共同组成 64 bit base 地址。</t>
+          <t>地址或 layout 变化时配置；低/高 32 bit 共同组成唯一地址组中的一个 64 bit base 地址。</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>每帧配置，低/高 32 bit 共同组成 64 bit base 地址。</t>
+          <t>地址或 layout 变化时配置；低/高 32 bit 共同组成唯一地址组中的一个 64 bit base 地址。</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>每帧配置，低/高 32 bit 共同组成 64 bit base 地址。</t>
+          <t>地址或 layout 变化时配置；低/高 32 bit 共同组成唯一地址组中的一个 64 bit base 地址。</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>每帧配置，低/高 32 bit 共同组成 64 bit base 地址。</t>
+          <t>地址或 layout 变化时配置；低/高 32 bit 共同组成唯一地址组中的一个 64 bit base 地址。</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>每帧配置，低/高 32 bit 共同组成 64 bit base 地址。</t>
+          <t>地址或 layout 变化时配置；低/高 32 bit 共同组成唯一地址组中的一个 64 bit base 地址。</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>每帧配置，低/高 32 bit 共同组成 64 bit base 地址。</t>
+          <t>地址或 layout 变化时配置；低/高 32 bit 共同组成唯一地址组中的一个 64 bit base 地址。</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>每帧配置；该高 32 bit 写入必须最后写，会提交当前四个 base 地址为一组帧地址。</t>
+          <t>地址或 layout 变化时配置；该高 32 bit 必须最后写，用于标记唯一地址组完整，随后写 START 锁存。</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>当前 slot 地址未配置错误 sticky 状态；ENC 数据链路按当前帧 fcnt[0] 选择 slot0 或 slot1 的地址配置。当硬件检查当前 slot 地址有效性时，如果被选中的地址 FIFO 为空，则 active_addr_cfg_valid 为 0，该 bit 置 1 并保持，同时参与 error IRQ。该状态表示当前帧没有可用的 META/TILE 基地址，软件必须先补齐对应 slot 的每帧地址组，确认 buffer 队列与 fcnt[0] 对齐后，再写 REG_IRQ_CTRL[1] irq_clear 清 sticky 状态；关闭 enc_ubwc_en 或硬复位也会清零。</t>
+          <t>单一地址配置无效 sticky 状态；数据链路检查地址时，如果最近一次 START 锁存的 META Y、TILE Y、META UV、TILE UV 地址组无效，则该 bit 置 1 并保持，同时参与 error IRQ。软件应按顺序重写完整地址组，写 START 锁存，再写 REG_IRQ_CTRL[1] irq_clear 清除旧错误。关闭 enc_ubwc_en 或硬复位也会清零。</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>addr_cfg_valid0</t>
+          <t>addr_cfg_valid</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ENC 地址 slot0 中存在已配置地址。</t>
+          <t>最近一次 START 已锁存一组完整有效的 META/TILE 基地址；后续帧持续复用，直到下一次 START 更新。</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>只读</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2746,17 +2746,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>addr_cfg_valid1</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>ENC 地址 slot1 中存在已配置地址。</t>
+          <t>保留，读回 0。</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>只读状态或统计信息。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>只读</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>addr_cfg_overflow</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>地址配置 FIFO overflow sticky 状态；ENC 每帧地址由 META Y、TILE Y、META UV、TILE UV 四个 64-bit 基地址组成，软件写 REG_TILE_BASE_UV_HI 作为一次地址组 commit。APB block 会按 slot0/slot1 轮流把地址组写入对应地址 FIFO，每个 slot FIFO 深度为 4。当 commit 时选中的 slot FIFO 已满，当前地址组不会 push 进 FIFO，该 bit 置 1 并保持，同时参与 error IRQ。软件应停止继续提交地址，等待已有帧消耗地址 FIFO；若已发生 overflow，应写 REG_IRQ_CTRL[1] irq_clear 清 sticky 状态，并确认软件 buffer 队列与硬件地址队列重新对齐，必要时关闭 enc_ubwc_en 后重新配置。</t>
+          <t>保留，读回 0。</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>只读状态或统计信息。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>0x005c</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>REG_STATUS1</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>7:0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stage_done</t>
+          <t>cfg_valid</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stage done 位图。</t>
+          <t>最近一次 START 配置提交结果；格式、尺寸、layout 和单一地址配置完整时为 1。为 0 时 ENC 保持 OTF 反压。</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>运行中读取。</t>
+          <t>只读状态或统计信息。</t>
         </is>
       </c>
     </row>
@@ -2909,17 +2909,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>REG_IRQ_CTRL</t>
+          <t>REG_STATUS1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>读写</t>
+          <t>只读</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2929,22 +2929,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7:0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>irq_enable</t>
+          <t>stage_done</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>中断使能；寄存器复位值为 0，需要中断输出时软件应配置为 1。</t>
+          <t>stage done 位图。</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>上电后或中断策略变化时配置。</t>
+          <t>运行中读取。</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>写 1 脉冲</t>
+          <t>读写</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2976,22 +2976,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>irq_clear</t>
+          <t>irq_enable</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>中断清除写 1 脉冲。</t>
+          <t>中断使能；寄存器复位值为 0，需要中断输出时软件应配置为 1。</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>软件处理中断后写 1；读回为 0。</t>
+          <t>上电后或中断策略变化时配置。</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>只读</t>
+          <t>写 1 脉冲</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3023,22 +3023,22 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>irq_pending</t>
+          <t>irq_clear</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>任意中断 pending 状态。</t>
+          <t>中断清除写 1 脉冲。</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>运行中或中断后读取，用于调试和状态确认。</t>
+          <t>软件处理中断后写 1；读回为 0。</t>
         </is>
       </c>
     </row>
@@ -3070,17 +3070,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>irq_correct_pending</t>
+          <t>irq_pending</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>正确完成中断 pending 状态。</t>
+          <t>任意中断 pending 状态。</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3117,17 +3117,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>irq_error_pending</t>
+          <t>irq_correct_pending</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>错误状态位。</t>
+          <t>正确完成中断 pending 状态。</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>写 1 脉冲</t>
+          <t>只读</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3164,22 +3164,22 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>irq_error_pending</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>帧 START 写 1 脉冲；地址组写完后再写该 bit 启动本帧。</t>
+          <t>错误状态位。</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>每帧地址组写完整后写 1；读回为 0。地址写入不再单独启动帧。</t>
+          <t>运行中或中断后读取，用于调试和状态确认。</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>读写</t>
+          <t>写 1 脉冲</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3211,22 +3211,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>vsync_reset_en</t>
+          <t>start</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ENC 输入 VSYNC 上升沿触发整条 ENC 链路软复位；复位通过 AXI drain reset sequencer 执行。</t>
+          <t>写 1 校验并锁存 ENC 配置快照，不启动帧。</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>按系统策略配置；置 1 后 ENC 输入 VSYNC 上升沿会触发软复位并重新 arm frame start。</t>
+          <t>静态配置和唯一地址组准备完成后写 1；再读取 STATUS0[14] cfg_valid 和 STATUS0[10] addr_cfg_valid。START 不启动帧。</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>只读</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3258,22 +3258,22 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>中断状态位图。</t>
+          <t>保留，读回 0。</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>运行中或中断后读取，用于调试和状态确认。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3305,22 +3305,22 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>中断状态位图。</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>只读状态或统计信息。</t>
+          <t>运行中或中断后读取，用于调试和状态确认。</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x006c</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x0078</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x007c</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x0080</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0084</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x0088</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x008c</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>0x0090</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>0x0094</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>0x0098</t>
+          <t>0x0094</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3896,47 +3896,94 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>只读</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>只读状态或统计信息。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>0x009c</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>只读</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>ENC 统计计数器；后缀 0/1 对应 fcnt[0] 地址 slot。</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ENC 统计计数器；后缀 0/1 仅按 fcnt[0] 分组统计，与地址选择无关。</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>只读状态或统计信息。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I82"/>
+  <autoFilter ref="A1:I83"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6439,7 +6486,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>帧 START 写 1 脉冲；地址组写完后再写该 bit 启动本帧。</t>
+          <t>写 1 产生 DEC decode START token。</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6760,7 +6807,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 13:09:24</t>
+          <t>2026-07-24 23:24:40</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6831,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>静态/几何/CI/VIVO/OTF timing 在图像格式、尺寸、layout 或 timing 变化时配置；地址组每帧配置。</t>
+          <t>ENC 静态/几何/CI 与唯一地址组在格式、尺寸、layout 或地址变化时配置并写 START 锁存；连续帧可复用。DEC 地址组仍按帧配置。</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6843,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -7322,7 +7369,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7332,7 +7379,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7347,14 +7394,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>配置下一帧地址组的 Y metadata base 低/高 32 bit；RGBA 使用该槽位存 RGBA metadata。</t>
+          <t>配置唯一一组 Y metadata base 低/高 32 bit；RGBA 使用该位置存 RGBA metadata。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7364,7 +7411,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7379,14 +7426,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>配置下一帧地址组的 Y tile data base 低/高 32 bit；RGBA 使用该槽位存 RGBA tile data。</t>
+          <t>配置唯一一组 Y tile data base 低/高 32 bit；RGBA 使用该位置存 RGBA tile data。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7396,7 +7443,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7411,14 +7458,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>配置 UV metadata base 低/高 32 bit，RGBA 写 0。</t>
+          <t>配置唯一一组 UV metadata base 低/高 32 bit，RGBA 写 0。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7428,7 +7475,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7443,14 +7490,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>配置 UV tile data base 低 32 bit，RGBA 写 0。</t>
+          <t>配置唯一一组 UV tile data base 低 32 bit，RGBA 写 0。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7460,7 +7507,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -7475,14 +7522,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>配置 UV tile data base 高 32 bit，RGBA 写 0。本写入会提交当前四个 64 bit base address 为一组帧地址，必须最后写。</t>
+          <t>配置 UV tile data base 高 32 bit，RGBA 写 0。该寄存器必须最后写，用于标记唯一工作地址组完整。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENC 启动</t>
+          <t>ENC 配置提交</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7492,7 +7539,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>每帧</t>
+          <t>静态配置或地址快照变化时</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -7507,14 +7554,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>写 START token。地址写入只填充地址队列，不再作为 start 标志；写 START 后再送入对应 OTF vsync/hsync/de/data。</t>
+          <t>写 START 提交并锁存完整配置快照。START 不复位也不启动帧；读取 STATUS0[14] cfg_valid。START 必须在目标 VSYNC 前完成。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENC 监控</t>
+          <t>ENC 帧启动</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7524,7 +7571,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>运行中</t>
+          <t>每帧</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -7534,19 +7581,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>READ 0x058/0x05C/0x060/0x064</t>
+          <t>输入 VSYNC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应 slot 没有可用地址配置，是 sticky 错误状态；软件补齐地址并确认队列对齐后，通过 REG_IRQ_CTRL[1] irq_clear 清除。IRQ bit 区分 correct/error pending。</t>
+          <t>每个 VSYNC 上升沿采样 cfg_valid，再触发 AXI drain 和全链路帧复位。采样有效时复位释放后自动运行；所有帧复用最近一次 START 锁存的唯一地址组。采样无效时整帧 o_otf_ready=0。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENC 清中断</t>
+          <t>ENC 监控</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7556,7 +7603,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>软件处理中断后</t>
+          <t>运行中</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -7566,29 +7613,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WRITE 0x060 bit[1]=1</t>
+          <t>READ 0x058/0x05C/0x060/0x064</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>清除 ENC 中断 pending。统计计数仍可用于调试。</t>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。cfg_valid 表示 START 提交结果；addr_cfg_valid 表示唯一地址组已锁存且有效；IRQ bit 区分 correct/error pending。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DEC 静态配置</t>
+          <t>ENC 清中断</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>ENC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>图像格式发生变化时配置</t>
+          <t>软件处理中断后</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7598,12 +7645,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WRITE 0x008 APB_ADDR_TILE_CFG0</t>
+          <t>WRITE 0x060 bit[1]=1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>配置 bank swizzle、bank spread、4-line format、lossy_rgba_2_1_format。这些配置在 frame start 时锁存到 AXI 域。</t>
+          <t>清除 ENC 中断 pending。统计计数仍可用于调试。</t>
         </is>
       </c>
     </row>
@@ -7630,19 +7677,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WRITE 0x00C APB_ADDR_TILE_CFG1</t>
+          <t>WRITE 0x008 APB_ADDR_TILE_CFG0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>配置 tile_cfg_pitch，单位 16 byte。</t>
+          <t>配置 bank swizzle、bank spread、4-line format、lossy_rgba_2_1_format。这些配置在 frame start 时锁存到 AXI 域。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DEC CI 配置</t>
+          <t>DEC 静态配置</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7662,19 +7709,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WRITE 0x010 APB_ADDR_TILE_CFG2</t>
+          <t>WRITE 0x00C APB_ADDR_TILE_CFG1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>配置 CI input type、lossy、alpha mode。寄存器复位值为 0，普通 tiled UBWC 路径软件应配置 ci_input_type=1。</t>
+          <t>配置 tile_cfg_pitch，单位 16 byte。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DEC VIVO 配置</t>
+          <t>DEC CI 配置</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7694,19 +7741,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WRITE 0x014 APB_ADDR_VIVO_CFG</t>
+          <t>WRITE 0x010 APB_ADDR_TILE_CFG2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>配置 vivo_ubwc_en 和 vivo_sreset。寄存器复位值为 0，启动 decode 前软件应配置 vivo_ubwc_en=1。</t>
+          <t>配置 CI input type、lossy、alpha mode。寄存器复位值为 0，普通 tiled UBWC 路径软件应配置 ci_input_type=1。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DEC 几何配置</t>
+          <t>DEC VIVO 配置</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7726,19 +7773,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>WRITE 0x018 APB_ADDR_OTF_CFG0</t>
+          <t>WRITE 0x014 APB_ADDR_VIVO_CFG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>配置输出 img_width 和 format，同时更新 meta_base_format。</t>
+          <t>配置 vivo_ubwc_en 和 vivo_sreset。寄存器复位值为 0，启动 decode 前软件应配置 vivo_ubwc_en=1。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DEC OTF timing</t>
+          <t>DEC 几何配置</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7758,12 +7805,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>WRITE 0x01C/0x020</t>
+          <t>WRITE 0x018 APB_ADDR_OTF_CFG0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>配置 h_total、h_sync、h_bp、h_act。输出 timing 不变时连续帧不需要重写。</t>
+          <t>配置输出 img_width 和 format，同时更新 meta_base_format。</t>
         </is>
       </c>
     </row>
@@ -7790,19 +7837,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>WRITE 0x024/0x028</t>
+          <t>WRITE 0x01C/0x020</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>配置 v_total、v_sync、v_bp、v_act。输出 timing 不变时连续帧不需要重写。</t>
+          <t>配置 h_total、h_sync、h_bp、h_act。输出 timing 不变时连续帧不需要重写。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEC 几何配置</t>
+          <t>DEC OTF timing</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7822,19 +7869,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>WRITE 0x02C APB_ADDR_META_CFG0</t>
+          <t>WRITE 0x024/0x028</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>配置 Y/RGBA 基准 metadata tile_x_numbers 和 tile_y_numbers；YUV420 的 UV metadata tile 数由格式内部推导。</t>
+          <t>配置 v_total、v_sync、v_bp、v_act。输出 timing 不变时连续帧不需要重写。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEC 每帧地址</t>
+          <t>DEC 几何配置</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7844,7 +7891,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>图像格式发生变化时配置</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -7854,12 +7901,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WRITE 0x030 then 0x034</t>
+          <t>WRITE 0x02C APB_ADDR_META_CFG0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>配置 RGBA/Y metadata base 低/高 32 bit。</t>
+          <t>配置 Y/RGBA 基准 metadata tile_x_numbers 和 tile_y_numbers；YUV420 的 UV metadata tile 数由格式内部推导。</t>
         </is>
       </c>
     </row>
@@ -7886,12 +7933,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WRITE 0x038 then 0x03C</t>
+          <t>WRITE 0x030 then 0x034</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>配置 RGBA/Y compressed tile base 低/高 32 bit。</t>
+          <t>配置 RGBA/Y metadata base 低/高 32 bit。</t>
         </is>
       </c>
     </row>
@@ -7918,12 +7965,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WRITE 0x040 then 0x044</t>
+          <t>WRITE 0x038 then 0x03C</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>配置 UV metadata base 低/高 32 bit。</t>
+          <t>配置 RGBA/Y compressed tile base 低/高 32 bit。</t>
         </is>
       </c>
     </row>
@@ -7950,19 +7997,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WRITE 0x048 then 0x04C</t>
+          <t>WRITE 0x040 then 0x044</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>配置 UV compressed tile base 低/高 32 bit，RGBA 图像不关心。</t>
+          <t>配置 UV metadata base 低/高 32 bit。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEC 启动</t>
+          <t>DEC 每帧地址</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7972,7 +8019,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>每帧</t>
+          <t>每帧都要配置</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7982,19 +8029,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WRITE 0x060 bit[5]=1</t>
+          <t>WRITE 0x048 then 0x04C</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>写 START token。完整地址组和 START token 都有效，且 metadata stage 可接受新帧时，硬件锁存本帧地址并启动 decode。</t>
+          <t>配置 UV compressed tile base 低/高 32 bit，RGBA 图像不关心。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEC 监控</t>
+          <t>DEC 启动</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8004,7 +8051,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>运行中</t>
+          <t>每帧</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8014,19 +8061,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>READ 0x050/0x054/0x060/0x064</t>
+          <t>WRITE 0x060 bit[5]=1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS4。STATUS1[4] 是 frame_done。STATUS4/IRQ_CTRL 区分 correct/error pending。</t>
+          <t>写 START token。完整地址组和 START token 都有效，且 metadata stage 可接受新帧时，硬件锁存本帧地址并启动 decode。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEC 统计</t>
+          <t>DEC 监控</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8036,7 +8083,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>运行中调试</t>
+          <t>运行中</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8046,121 +8093,121 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>READ 0x068/0x06C/0x070/0x074/0x078</t>
+          <t>READ 0x050/0x054/0x060/0x064</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>读取 metadata tile count、tile address count、OTF tile count、OTF line count、OTF de beat count。</t>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS4。STATUS1[4] 是 frame_done。STATUS4/IRQ_CTRL 区分 correct/error pending。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>DEC 统计</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>运行中调试</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>READ 0x068/0x06C/0x070/0x074/0x078</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>读取 metadata tile count、tile address count、OTF tile count、OTF line count、OTF de beat count。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>DEC 清中断</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>软件处理中断后</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>WRITE 0x060 bit[1]=1</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>清除 DEC 中断 pending。VIVO idle/error 状态和统计计数仍可读。</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>格式</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>编码</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>tile_w</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>tile_h</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>bpp</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>配置复用说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>RGBA8888</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>格式和尺寸不变时，tile/OTF/meta geometry 可复用；每帧只更新 base address。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RGBA1010102</t>
+          <t>RGBA8888</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8180,83 +8227,115 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>几何规则同 RGBA8888；只换 buffer 地址时不需要重配 geometry。</t>
+          <t>格式、尺寸和输出 buffer 不变时，静态配置与唯一地址组均可持续复用。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>YUV420_8/NV12</t>
+          <t>RGBA1010102</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1(Y),2(UV pair)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Y/UV 有独立 metadata/tile base；新 buffer 必须写每帧地址。</t>
+          <t>几何规则同 RGBA8888；更换 buffer 地址后重新写完整地址组并写 START。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>YUV420_8/NV12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1(Y),2(UV pair)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Y/UV 使用唯一一组独立 metadata/tile base；地址变化后重新写完整地址组并写 START。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>YUV420_10/P010</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>2(Y),4(UV pair)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>tile count 规则按 P010 tile_h=4 计算，pitch 使用 16 bit component 存储计算。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F46"/>
+  <autoFilter ref="A1:F47"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="120" customWidth="1"/>
@@ -8290,12 +8369,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ENC 地址 slot</t>
+          <t>ENC 唯一地址组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ENC 使用两个交替地址 slot，对应 fcnt[0]=0/1。每项包含 Y metadata base、Y tile base、UV metadata base、UV tile base。</t>
+          <t>ENC 仅保留一组 Y metadata、Y tile、UV metadata、UV tile base；fcnt 不参与地址选择。</t>
         </is>
       </c>
     </row>
@@ -8307,60 +8386,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>每帧写完四个 64-bit base 后，最后写 REG_TILE_BASE_UV_HI @0x04C。该写入会提交当前四个 base 为一组帧地址。</t>
+          <t>四个 64-bit base 写完后，最后写 REG_TILE_BASE_UV_HI @0x04C 标记工作地址组完整；再写 IRQ_CTRL[5] START 锁存快照，并读取 STATUS0[14] cfg_valid 和 STATUS0[10] addr_cfg_valid。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEC 地址组</t>
+          <t>ENC 帧控制</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEC 每帧写 metadata/tile 的 RGBA/Y 与 UV base 地址。完整地址组有效后可启动 decode。</t>
+          <t>每个输入 VSYNC 上升沿采样配置有效性并触发 AXI drain 和帧级全链路复位；采样有效时复位释放后自动运行。连续帧复用同一地址，直到下一次 START 更新。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEC START</t>
+          <t>DEC 地址组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>完整 DEC 地址组和 START token 都有效、metadata 不 busy、launch slot 可用时，硬件锁存本帧地址并启动 decode。</t>
+          <t>DEC 每帧写 metadata/tile 的 RGBA/Y 与 UV base 地址。完整地址组有效后可启动 decode。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>连续 layout</t>
+          <t>DEC START</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YUV 通常按 Y metadata、Y tile data、UV metadata、UV tile data 连续排列。RGBA 只需要 RGBA metadata 和 RGBA tile data。</t>
+          <t>完整 DEC 地址组和 START token 都有效、metadata 不 busy、launch slot 可用时，硬件锁存本帧地址并启动 decode。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>连续 layout</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>YUV 通常按 Y metadata、Y tile data、UV metadata、UV tile data 连续排列。RGBA 只需要 RGBA metadata 和 RGBA tile data。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>中断</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>correct IRQ/frame_done 在最后一个有效帧输出/数据完成事件后产生；error IRQ 在错误条件锁存时产生。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>